--- a/output/pdf_financials_xlsx/BTR.xlsx
+++ b/output/pdf_financials_xlsx/BTR.xlsx
@@ -6887,70 +6887,44 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>1.972071</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>2.001744</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>2.029686</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>2.346061</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>4.421229</v>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>7.6772</v>
+      </c>
+      <c r="H107" s="3" t="n">
+        <v>7.810473</v>
+      </c>
+      <c r="I107" s="3" t="n">
+        <v>12.731888</v>
+      </c>
+      <c r="J107" s="3" t="n">
+        <v>18.681388</v>
+      </c>
+      <c r="K107" s="3" t="n">
+        <v>20.252388</v>
+      </c>
+      <c r="L107" s="3" t="n">
+        <v>20.962388</v>
+      </c>
+      <c r="M107" s="3" t="n">
+        <v>25.031153</v>
+      </c>
+      <c r="N107" s="3" t="n">
+        <v>27.202378</v>
       </c>
     </row>
     <row r="108">
@@ -8158,13 +8132,13 @@
         <v>1e-06</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>0</v>
+        <v>-0.152229</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>0</v>
+        <v>-4.36626</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>0</v>
+        <v>-9.76149</v>
       </c>
       <c r="H133" s="3" t="n">
         <v>0</v>
@@ -10203,7 +10177,11 @@
           <t>Share-based payments reserve (note 16)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -10677,7 +10655,11 @@
           <t>Share-based payments reserve (note 16)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -11368,7 +11350,11 @@
           <t>Share-based Payments Reserve (note 17)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -12783,7 +12769,11 @@
           <t>Share-based Payments Reserve (note 22) 14,026,388</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -14425,7 +14415,11 @@
           <t>Share-based Payments Reserve (note 22)</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -15257,7 +15251,11 @@
           <t>Share-based Payments Reserve (note 13) 7,810,473</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -16247,7 +16245,11 @@
           <t>Share-based Payments Reserve (note 11)</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -17063,7 +17065,11 @@
           <t>Share-based Payments Reserve (note 13)</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -18383,7 +18389,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E116" s="5" t="n">
         <v>1.972071</v>
       </c>
@@ -29713,7 +29723,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BTR.xlsx
+++ b/output/pdf_financials_xlsx/BTR.xlsx
@@ -540,11 +540,15 @@
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>9.1e-05</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>0.000145</v>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
@@ -561,11 +565,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G4" s="3" t="n">
-        <v>0.015029</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>0.015029</v>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
@@ -1283,10 +1291,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1.217308</v>
+        <v>3.231083</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.85515</v>
+        <v>6.86092</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>0.366374</v>
@@ -1379,10 +1387,10 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0</v>
+        <v>9.1e-05</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0</v>
+        <v>0.000145</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>0</v>
@@ -1394,10 +1402,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0</v>
+        <v>0.015029</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0</v>
+        <v>0.015029</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>0</v>
@@ -2121,10 +2129,10 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>-2.782706</v>
+        <v>-2.782797</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>-6.771966</v>
+        <v>-6.772111</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>-0.537538</v>
@@ -2136,10 +2144,10 @@
         <v>-3.339047</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>-3.381233</v>
+        <v>-3.396262</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>-22.00286</v>
+        <v>-22.017889</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>-100.843563</v>
@@ -2213,10 +2221,10 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>-2.782706</v>
+        <v>-2.782797</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-6.771966</v>
+        <v>-6.772111</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>-0.537538</v>
@@ -2228,10 +2236,10 @@
         <v>-3.339047</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>-3.381233</v>
+        <v>-3.396262</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>-21.742305</v>
+        <v>-21.757334</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>-99.71202599999999</v>
@@ -2889,15 +2897,11 @@
       <c r="C46" s="3" t="n">
         <v>0.016058</v>
       </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D46" s="3" t="n">
+        <v>0.00205</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0.098606</v>
       </c>
       <c r="F46" s="3" t="n">
         <v>0.351029</v>
@@ -2911,20 +2915,14 @@
       <c r="I46" s="3" t="n">
         <v>9.806590999999999</v>
       </c>
-      <c r="J46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J46" s="3" t="n">
+        <v>4.479221</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>7.394113</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>2.793796</v>
       </c>
       <c r="M46" s="3" t="n">
         <v>1.211478</v>
@@ -3002,12 +3000,10 @@
         <v>0.016058</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.128425</v>
-      </c>
-      <c r="E48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.130475</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0.098606</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.351029</v>
@@ -3022,13 +3018,13 @@
         <v>9.826591000000001</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.06</v>
+        <v>4.539221</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.06</v>
+        <v>7.454113</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.06</v>
+        <v>2.853796</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>1.233083</v>
@@ -3820,10 +3816,10 @@
         <v>0.019908</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>0.00205</v>
+        <v>0</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>0.123711</v>
+        <v>0.025105</v>
       </c>
       <c r="F60" s="3" t="n">
         <v>0.10869</v>
@@ -3838,13 +3834,13 @@
         <v>2.013817</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>4.479221</v>
+        <v>0</v>
       </c>
       <c r="K60" s="3" t="n">
-        <v>7.394113</v>
+        <v>0</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>2.914759</v>
+        <v>0.120963</v>
       </c>
       <c r="M60" s="3" t="n">
         <v>0.809976</v>
@@ -10499,7 +10495,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -11433,7 +11429,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -11516,7 +11512,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -17146,7 +17142,11 @@
           <t>Reclamation Deposit (note 8)</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -30288,7 +30288,11 @@
           <t>Write-down of reclamation deposit</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E265" t="inlineStr">
         <is>
           <t>-</t>
@@ -42324,7 +42328,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -43470,7 +43474,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -46376,14 +46380,14 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E465" s="5" t="n">
-        <v>-3.231083</v>
+        <v>3.231083</v>
       </c>
       <c r="F465" s="5" t="n">
-        <v>-6.86092</v>
+        <v>6.86092</v>
       </c>
       <c r="G465" t="inlineStr">
         <is>
@@ -46459,7 +46463,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E466" s="5" t="n">

--- a/output/pdf_financials_xlsx/BTR.xlsx
+++ b/output/pdf_financials_xlsx/BTR.xlsx
@@ -1162,34 +1162,34 @@
         <v>0.366374</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.6910770000000001</v>
+        <v>0.904271</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.747278</v>
+        <v>1.951778</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2.514367</v>
+        <v>3.255367</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>4.125097</v>
+        <v>4.889097</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>5.614073</v>
+        <v>8.800423</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.722685</v>
+        <v>1.66664</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.538521</v>
+        <v>3.156268</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.419113</v>
+        <v>2.197062</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>0.77755</v>
+        <v>2.343279</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>0.657486</v>
+        <v>2.1493</v>
       </c>
     </row>
     <row r="14">
@@ -1300,34 +1300,34 @@
         <v>0.366374</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.6910770000000001</v>
+        <v>0.904271</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.747278</v>
+        <v>1.951778</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2.514367</v>
+        <v>3.255367</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>4.125097</v>
+        <v>4.889097</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>5.614073</v>
+        <v>8.800423</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.722685</v>
+        <v>1.66664</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.538521</v>
+        <v>3.156268</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.419113</v>
+        <v>2.197062</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.77755</v>
+        <v>2.343279</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.657486</v>
+        <v>2.1493</v>
       </c>
     </row>
     <row r="17">
@@ -1828,7 +1828,7 @@
         <v>-22.00286</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-100.843563</v>
+        <v>-91.70734400000001</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>-31.920324</v>
@@ -1874,7 +1874,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0</v>
+        <v>-9.136219000000001</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>0</v>
@@ -5081,40 +5081,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H79" s="3" t="n">
+        <v>0.303036</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>3.136794</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>0.730287</v>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>1.364975</v>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>0.913903</v>
+      </c>
+      <c r="M79" s="3" t="n">
+        <v>0.792476</v>
+      </c>
+      <c r="N79" s="3" t="n">
+        <v>0.765582</v>
       </c>
     </row>
     <row r="80">
@@ -5142,25 +5128,25 @@
         <v>1.214714</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>3.338873</v>
+        <v>3.641909</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>8.663645000000001</v>
+        <v>11.800439</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>5.335221</v>
+        <v>6.065508</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>6.576871</v>
+        <v>7.941846</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>6.98762</v>
+        <v>7.901523</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>2.570705</v>
+        <v>3.363181</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>2.536648</v>
+        <v>3.30223</v>
       </c>
     </row>
     <row r="81">
@@ -5608,25 +5594,29 @@
         <v>0.385436</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>3.469531</v>
+        <v>3.166495</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>7.254</v>
+        <v>4.117206</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>2.998</v>
+        <v>2.267713</v>
       </c>
       <c r="K87" s="3" t="n">
-        <v>3.940144</v>
-      </c>
-      <c r="L87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" s="3" t="n">
-        <v>0.426</v>
+        <v>2.575169</v>
+      </c>
+      <c r="L87" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M87" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N87" s="3" t="n">
-        <v>15.266488</v>
+        <v>14.500906</v>
       </c>
     </row>
     <row r="88">
@@ -7772,22 +7762,22 @@
         <v>0</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>0.147</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>0.214</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>0.343</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>0.415</v>
       </c>
     </row>
     <row r="126">
@@ -7797,10 +7787,10 @@
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>0</v>
+        <v>-0.003825</v>
       </c>
       <c r="C126" s="3" t="n">
-        <v>0</v>
+        <v>-0.003597</v>
       </c>
       <c r="D126" s="3" t="n">
         <v>0</v>
@@ -7812,7 +7802,7 @@
         <v>0</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>0</v>
+        <v>-0.026678</v>
       </c>
       <c r="H126" s="3" t="n">
         <v>-2.861472</v>
@@ -7953,10 +7943,10 @@
         <v>0</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="I129" s="3" t="n">
-        <v>0</v>
+        <v>1.257975</v>
       </c>
       <c r="J129" s="3" t="n">
         <v>0</v>
@@ -7987,10 +7977,10 @@
         <v>0</v>
       </c>
       <c r="D130" s="3" t="n">
-        <v>0</v>
+        <v>0.104717</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>0</v>
+        <v>0.119813</v>
       </c>
       <c r="F130" s="3" t="n">
         <v>0</v>
@@ -8881,10 +8871,10 @@
         </is>
       </c>
       <c r="B149" s="3" t="n">
-        <v>0</v>
+        <v>-0.003825</v>
       </c>
       <c r="C149" s="3" t="n">
-        <v>0</v>
+        <v>-0.003597</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>0</v>
@@ -8896,7 +8886,7 @@
         <v>0</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>0</v>
+        <v>-0.026678</v>
       </c>
       <c r="H149" s="3" t="n">
         <v>-2.861472</v>
@@ -8927,10 +8917,10 @@
         </is>
       </c>
       <c r="B150" s="3" t="n">
-        <v>-1.508807</v>
+        <v>-1.512632</v>
       </c>
       <c r="C150" s="3" t="n">
-        <v>-0.683066</v>
+        <v>-0.686663</v>
       </c>
       <c r="D150" s="3" t="n">
         <v>-0.686057</v>
@@ -8942,7 +8932,7 @@
         <v>-2.417257</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>-3.58538</v>
+        <v>-3.612058</v>
       </c>
       <c r="H150" s="3" t="n">
         <v>-30.556031</v>
@@ -19068,7 +19058,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -21809,7 +21803,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -23022,7 +23020,11 @@
           <t>Accretion expense 80,000</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -26341,7 +26343,11 @@
           <t>Sale (Purchase) of marketable securities</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -29804,7 +29810,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E259" s="5" t="n">
         <v>-0.003825</v>
       </c>
@@ -30452,7 +30462,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -33909,7 +33923,11 @@
           <t>Salaries, management and director fees (note 13)</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
           <t>-</t>
@@ -36944,7 +36962,11 @@
           <t>Salaries, management and director fees (note 16) 1,076,724</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
@@ -38590,7 +38612,11 @@
           <t>Net Loss from Discontinued Operations (note 24) (343,000)</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E369" t="inlineStr">
         <is>
           <t>-</t>
@@ -39406,7 +39432,11 @@
           <t>Salaries, management and director fees (note 16)</t>
         </is>
       </c>
-      <c r="D379" t="inlineStr"/>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
           <t>-</t>
@@ -40522,7 +40552,11 @@
           <t>Net Loss from Continuing Operations</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E393" t="inlineStr">
         <is>
           <t>-</t>
@@ -40601,7 +40635,11 @@
           <t>Net Loss from Discontinued Operations (note 24)</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E394" t="inlineStr">
         <is>
           <t>-</t>
@@ -41488,7 +41526,11 @@
           <t>Management and director fees (note 12) 764,000</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr"/>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E405" t="inlineStr">
         <is>
           <t>-</t>
@@ -42986,7 +43028,11 @@
           <t>Management and director fees (note 10)</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E423" t="inlineStr">
         <is>
           <t>-</t>
@@ -43877,7 +43923,11 @@
           <t>Management and director fees (note 12)</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr">
         <is>
           <t>-</t>
